--- a/data/iuran_sosial.xlsx
+++ b/data/iuran_sosial.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -472,46 +472,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>dc125234-a61c-4b31-8e50-5d2f88c0e8e0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AGT-065</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-04-23 08:39:57</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Catatan iuran sosial (tidak menambah saldo simpanan)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
